--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{582C5957-D2C2-4B47-A31F-E6CBDA90DF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58861C0-1820-4FB7-BA7A-4AED5993E872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="3180" windowWidth="28410" windowHeight="15345" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="780" yWindow="3180" windowWidth="28020" windowHeight="14100" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -107,9 +107,6 @@
     <t>Madrass</t>
   </si>
   <si>
-    <t>Sovsäck</t>
-  </si>
-  <si>
     <t>Kudde</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>Tandkräm</t>
   </si>
   <si>
-    <t>Nagelklippare</t>
-  </si>
-  <si>
     <t>Solskydd</t>
   </si>
   <si>
@@ -309,6 +303,12 @@
   </si>
   <si>
     <t>Rakhyvel + parfym + skyddsfodral</t>
+  </si>
+  <si>
+    <t>Nagelklippare, pincett</t>
+  </si>
+  <si>
+    <t>Sovsäck, lätt</t>
   </si>
 </sst>
 </file>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
@@ -748,7 +748,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -883,10 +883,10 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
@@ -902,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
@@ -918,7 +918,7 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -942,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -950,20 +950,20 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1025,15 +1025,18 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>1</v>
+      </c>
       <c r="B48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -1041,12 +1044,12 @@
         <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -1054,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
@@ -1062,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
@@ -1070,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -1078,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
@@ -1086,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -1094,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -1102,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
@@ -1110,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -1118,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
@@ -1126,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -1134,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -1142,12 +1145,12 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1155,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1163,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1179,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1187,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -1195,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -1203,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -1211,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -1222,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -1230,12 +1233,12 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -1243,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -1251,7 +1254,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -1259,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.2">
@@ -1267,7 +1270,7 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.2">
@@ -1275,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -1283,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
@@ -1291,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.2">
@@ -1307,7 +1310,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.2">
@@ -1315,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.2">
@@ -1323,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.2">
@@ -1331,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.2">
@@ -1339,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.2">
@@ -1347,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.2">
@@ -1355,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.2">
@@ -1363,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.2">
@@ -1371,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.2">
@@ -1379,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.2">
@@ -1387,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.2">
@@ -1395,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58861C0-1820-4FB7-BA7A-4AED5993E872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37F60BEF-D1CF-4CAE-A69E-19A21D2D1CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="3180" windowWidth="28020" windowHeight="14100" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="2805" yWindow="2595" windowWidth="26640" windowHeight="15120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -215,9 +215,6 @@
     <t>Desinfektion</t>
   </si>
   <si>
-    <t>Handskar för meck</t>
-  </si>
-  <si>
     <t>Tire levers</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>Sovsäck, lätt</t>
+  </si>
+  <si>
+    <t>Handskar för meck, de tunna</t>
   </si>
 </sst>
 </file>
@@ -686,26 +686,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363B01-F3E6-4FE4-8E68-4A80D3197864}">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A2:D99"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B1">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>70</v>
-      </c>
-    </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
@@ -713,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
@@ -721,34 +713,31 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
-        <v>0</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
+      <c r="C7" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
@@ -756,28 +745,31 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C13" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
@@ -785,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
@@ -793,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
@@ -801,15 +793,15 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -817,20 +809,20 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -838,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
@@ -846,31 +838,31 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.2">
@@ -878,23 +870,23 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
@@ -902,31 +894,31 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C32" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C33" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -934,15 +926,15 @@
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -950,20 +942,20 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C39" s="1" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C40" s="1" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -971,45 +963,45 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>1</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43" t="s">
-        <v>89</v>
-      </c>
-    </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>1</v>
-      </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1017,148 +1009,148 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B48">
         <v>2</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>1</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>1</v>
+      </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C51" s="1" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C52" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C65" s="1" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C66" s="1" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1166,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1174,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1182,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -1198,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -1206,79 +1198,79 @@
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B74">
         <v>3</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>1</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C77" s="1" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C78" s="1" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -1286,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
@@ -1294,31 +1286,31 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.2">
@@ -1326,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.2">
@@ -1334,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.2">
@@ -1342,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.2">
@@ -1350,39 +1342,39 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.2">
@@ -1390,19 +1382,27 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="C98" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B98">
+  <conditionalFormatting sqref="B2:B99">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37F60BEF-D1CF-4CAE-A69E-19A21D2D1CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AB4FC0-6ADB-4319-896C-00CBB721133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="2595" windowWidth="26640" windowHeight="15120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
   <si>
     <t>Cykel</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Chamoiskräm</t>
   </si>
   <si>
-    <t>Överigt</t>
-  </si>
-  <si>
     <t>Ficklampa</t>
   </si>
   <si>
@@ -309,6 +306,18 @@
   </si>
   <si>
     <t>Handskar för meck, de tunna</t>
+  </si>
+  <si>
+    <t>Övrigt</t>
+  </si>
+  <si>
+    <t>Kedjelänk</t>
+  </si>
+  <si>
+    <t>Handkräm</t>
+  </si>
+  <si>
+    <t>Munspel??</t>
   </si>
 </sst>
 </file>
@@ -686,50 +695,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363B01-F3E6-4FE4-8E68-4A80D3197864}">
-  <dimension ref="A2:D99"/>
+  <dimension ref="A2:G75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>0</v>
       </c>
@@ -739,8 +783,14 @@
       <c r="D8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
@@ -750,37 +800,75 @@
       <c r="D9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>0</v>
       </c>
@@ -788,84 +876,149 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="G16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>1</v>
       </c>
@@ -873,44 +1026,83 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="G28" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>2</v>
       </c>
@@ -920,61 +1112,117 @@
       <c r="D34" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1</v>
       </c>
@@ -984,16 +1232,28 @@
       <c r="C43" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1003,24 +1263,42 @@
       <c r="C45" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>2</v>
       </c>
@@ -1028,7 +1306,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1</v>
       </c>
@@ -1036,373 +1314,41 @@
         <v>0</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C52" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C66" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B74">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51">
         <v>3</v>
       </c>
-      <c r="C74" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="C76" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C78" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="C79" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B80">
-        <v>2</v>
-      </c>
-      <c r="C80" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="C81" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="C83" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B86">
-        <v>2</v>
-      </c>
-      <c r="C86" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B87">
-        <v>3</v>
-      </c>
-      <c r="C87" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="C90" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="C91" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="C92" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B95">
-        <v>0</v>
-      </c>
-      <c r="C95" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="C97" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="C99" t="s">
-        <v>78</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B99">
+  <conditionalFormatting sqref="B2:B51 F51 F2:F49">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AB4FC0-6ADB-4319-896C-00CBB721133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5333F711-4457-4BF8-BF7B-D6CF2850445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -903,7 +903,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5333F711-4457-4BF8-BF7B-D6CF2850445E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C3E7470-6429-4E64-AD1E-4B8C1E4A6F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Packning" sheetId="1" r:id="rId1"/>
+    <sheet name="Bingo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="119">
   <si>
     <t>Cykel</t>
   </si>
@@ -44,12 +45,6 @@
     <t>Cykellås</t>
   </si>
   <si>
-    <t>hållare</t>
-  </si>
-  <si>
-    <t>Flaskhållare * 2</t>
-  </si>
-  <si>
     <t>Cykellampa</t>
   </si>
   <si>
@@ -68,9 +63,6 @@
     <t>Snackväska</t>
   </si>
   <si>
-    <t>Toptubebag?</t>
-  </si>
-  <si>
     <t>Verktyg</t>
   </si>
   <si>
@@ -92,15 +84,9 @@
     <t>Kattstrypare</t>
   </si>
   <si>
-    <t>Reservdelar?</t>
-  </si>
-  <si>
     <t>Övernattning</t>
   </si>
   <si>
-    <t>Tält</t>
-  </si>
-  <si>
     <t>Regnskydd</t>
   </si>
   <si>
@@ -110,12 +96,6 @@
     <t>Kudde</t>
   </si>
   <si>
-    <t>Tältpinnar</t>
-  </si>
-  <si>
-    <t>Vattenflaskor</t>
-  </si>
-  <si>
     <t>Toalettartiklar</t>
   </si>
   <si>
@@ -146,9 +126,6 @@
     <t>Powerbank</t>
   </si>
   <si>
-    <t>Hörlurar + laddare</t>
-  </si>
-  <si>
     <t>Klocka + laddare</t>
   </si>
   <si>
@@ -158,24 +135,12 @@
     <t>Matlagning</t>
   </si>
   <si>
-    <t>Primus</t>
-  </si>
-  <si>
-    <t>Diskmedel</t>
-  </si>
-  <si>
-    <t>Bestick</t>
-  </si>
-  <si>
     <t>Spork</t>
   </si>
   <si>
     <t>Mikrofiberduk</t>
   </si>
   <si>
-    <t>Disktrasa</t>
-  </si>
-  <si>
     <t>Kläder</t>
   </si>
   <si>
@@ -185,9 +150,6 @@
     <t>Cykeltröjor</t>
   </si>
   <si>
-    <t>Casualtröja</t>
-  </si>
-  <si>
     <t>Strumpor * 3</t>
   </si>
   <si>
@@ -200,9 +162,6 @@
     <t>Casualshorts / Byxor</t>
   </si>
   <si>
-    <t>Vandringsbyxor</t>
-  </si>
-  <si>
     <t>Långärmad merino</t>
   </si>
   <si>
@@ -233,9 +192,6 @@
     <t>Barefootskor</t>
   </si>
   <si>
-    <t>Olja, salt, peppar</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -278,9 +234,6 @@
     <t>Hörproppar</t>
   </si>
   <si>
-    <t>Derailleur??</t>
-  </si>
-  <si>
     <t>Plinga</t>
   </si>
   <si>
@@ -317,14 +270,137 @@
     <t>Handkräm</t>
   </si>
   <si>
-    <t>Munspel??</t>
+    <t>Kasse</t>
+  </si>
+  <si>
+    <t>Tvättmedel</t>
+  </si>
+  <si>
+    <t>Flaskhållare * 2 + flaska</t>
+  </si>
+  <si>
+    <t>Toptubebag</t>
+  </si>
+  <si>
+    <t>ej</t>
+  </si>
+  <si>
+    <t>Reservdelar</t>
+  </si>
+  <si>
+    <t>Derailleur</t>
+  </si>
+  <si>
+    <t>Tält + pinnar</t>
+  </si>
+  <si>
+    <t>Hörlurar</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>Salt, peppar</t>
+  </si>
+  <si>
+    <t>2xCasualtröja</t>
+  </si>
+  <si>
+    <t>Färgpennor</t>
+  </si>
+  <si>
+    <t>Munspel</t>
+  </si>
+  <si>
+    <t>Lätta vandringsbyxor</t>
+  </si>
+  <si>
+    <t>Pennfodral</t>
+  </si>
+  <si>
+    <t>Packbar ryggsäck</t>
+  </si>
+  <si>
+    <t>Smaka ett närproducerat vin</t>
+  </si>
+  <si>
+    <t>Besöka en fabrik</t>
+  </si>
+  <si>
+    <t>Delta i någon</t>
+  </si>
+  <si>
+    <t>Måla av en turistattraktion</t>
+  </si>
+  <si>
+    <t>Prata med en polis</t>
+  </si>
+  <si>
+    <t>Ta en bild utanför Colosseum</t>
+  </si>
+  <si>
+    <t>Bestig ett berg</t>
+  </si>
+  <si>
+    <t>Träffa en 100-åring</t>
+  </si>
+  <si>
+    <t>Spring en marathon</t>
+  </si>
+  <si>
+    <t>Gör en snöängel</t>
+  </si>
+  <si>
+    <t>Se på en fotbollsmatch</t>
+  </si>
+  <si>
+    <t>Testkör en Ferrari eller Fiat</t>
+  </si>
+  <si>
+    <t>Ät något du aldrig smakat förut</t>
+  </si>
+  <si>
+    <t>Testa någon ny sport som du aldrig gjort</t>
+  </si>
+  <si>
+    <t>Besök alla regioner</t>
+  </si>
+  <si>
+    <t>Besök Pompeii</t>
+  </si>
+  <si>
+    <t>Gå ombord på en lyxbåt</t>
+  </si>
+  <si>
+    <t>Se en konsert eller ett liveband</t>
+  </si>
+  <si>
+    <t>Springa runt ett land</t>
+  </si>
+  <si>
+    <t>Bada i 5 olika hav</t>
+  </si>
+  <si>
+    <t>Bestig Etna eller Vesuvius</t>
+  </si>
+  <si>
+    <t>Kolla Giro d'Italia live</t>
+  </si>
+  <si>
+    <t>Gå in i ett kasino i Monaco</t>
+  </si>
+  <si>
+    <t>Bild med kändis</t>
+  </si>
+  <si>
+    <t>Delta i en tävling</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -333,6 +409,11 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="SK Sans"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="SK Sans"/>
@@ -358,9 +439,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
@@ -717,13 +802,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
@@ -731,13 +816,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
@@ -745,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
@@ -759,7 +844,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
@@ -770,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
@@ -780,45 +865,39 @@
       <c r="C8" t="s">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
@@ -826,13 +905,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
         <v>81</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -840,18 +922,18 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
@@ -859,13 +941,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -873,7 +955,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
@@ -881,256 +969,257 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
         <v>11</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G29" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D30" s="1"/>
       <c r="F30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>0</v>
+      </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C33" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" t="s">
-        <v>24</v>
+      <c r="C34" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
       <c r="B35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -1138,74 +1227,80 @@
         <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38">
         <v>2</v>
       </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="F37">
+      <c r="G38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39">
         <v>3</v>
       </c>
-      <c r="G37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>2</v>
-      </c>
-      <c r="C38" t="s">
-        <v>23</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C40" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41" t="s">
-        <v>27</v>
+      <c r="C41" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -1213,30 +1308,27 @@
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>1</v>
-      </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -1244,44 +1336,44 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="B45">
         <v>1</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -1289,38 +1381,38 @@
         <v>0</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49">
         <v>2</v>
       </c>
-      <c r="C48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>1</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
       <c r="C49" t="s">
-        <v>86</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -1328,18 +1420,49 @@
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>70</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>0</v>
+      </c>
       <c r="C51" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F51">
-        <v>3</v>
-      </c>
-      <c r="G51" t="s">
-        <v>93</v>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
@@ -1348,7 +1471,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B51 F51 F2:F49">
+  <conditionalFormatting sqref="B2:B52 F2:F48 F50:F53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1362,4 +1485,102 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51904074-9142-4DAA-A0F8-B1C4998D9D30}">
+  <dimension ref="B2:F6"/>
+  <sheetFormatPr defaultColWidth="15.25" defaultRowHeight="80.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="15.25" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C3E7470-6429-4E64-AD1E-4B8C1E4A6F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C92B807-B629-4100-8E75-93DD61B36BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
@@ -327,9 +327,6 @@
     <t>Besöka en fabrik</t>
   </si>
   <si>
-    <t>Delta i någon</t>
-  </si>
-  <si>
     <t>Måla av en turistattraktion</t>
   </si>
   <si>
@@ -363,9 +360,6 @@
     <t>Testa någon ny sport som du aldrig gjort</t>
   </si>
   <si>
-    <t>Besök alla regioner</t>
-  </si>
-  <si>
     <t>Besök Pompeii</t>
   </si>
   <si>
@@ -390,10 +384,16 @@
     <t>Gå in i ett kasino i Monaco</t>
   </si>
   <si>
-    <t>Bild med kändis</t>
-  </si>
-  <si>
     <t>Delta i en tävling</t>
+  </si>
+  <si>
+    <t>Delta i någonting udda</t>
+  </si>
+  <si>
+    <t>Bli helt och hållet dyngsur av regn</t>
+  </si>
+  <si>
+    <t>Ta en bild med kändis</t>
   </si>
 </sst>
 </file>
@@ -439,12 +439,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1496,87 +1499,87 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>94</v>
       </c>
     </row>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C92B807-B629-4100-8E75-93DD61B36BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04DCD7BF-1C54-4A05-BACB-BF3E57ACE117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="14205" yWindow="3090" windowWidth="15285" windowHeight="14880" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Packning" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>Cykel</t>
   </si>
@@ -910,11 +910,8 @@
       <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="s">
         <v>64</v>
@@ -1254,28 +1251,22 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>86</v>
-      </c>
       <c r="B38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C38" t="s">
         <v>72</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>86</v>
-      </c>
       <c r="B39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -1350,7 +1341,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="s">
         <v>71</v>
@@ -1454,7 +1445,7 @@
         <v>76</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>92</v>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04DCD7BF-1C54-4A05-BACB-BF3E57ACE117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BFED1A5-34EE-4281-B90B-5EA3CFBBBC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14205" yWindow="3090" windowWidth="15285" windowHeight="14880" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Packning" sheetId="1" r:id="rId1"/>
     <sheet name="Bingo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <t>Cykel</t>
   </si>
@@ -783,679 +784,742 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363B01-F3E6-4FE4-8E68-4A80D3197864}">
-  <dimension ref="A2:G75"/>
+  <dimension ref="A2:I75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5" t="s">
         <v>54</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C13" s="1" t="s">
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
         <v>4</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
         <v>7</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
         <v>86</v>
       </c>
-      <c r="F17">
+      <c r="G19">
         <v>3</v>
       </c>
-      <c r="G17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="H19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>60</v>
       </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C21" s="1" t="s">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
         <v>9</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B23">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>10</v>
       </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
         <v>11</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>81</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>2</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>14</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>81</v>
       </c>
-      <c r="B30">
+      <c r="B47">
         <v>2</v>
       </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44">
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
-      <c r="G44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45" t="s">
-        <v>71</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="H47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>81</v>
       </c>
-      <c r="B46">
+      <c r="B50">
         <v>2</v>
       </c>
-      <c r="C46" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49">
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50">
         <v>2</v>
       </c>
-      <c r="C49" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="H50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51" t="s">
         <v>70</v>
       </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="G50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
         <v>43</v>
       </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
         <v>76</v>
       </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1465,7 +1529,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B52 F2:F48 F50:F53">
+  <conditionalFormatting sqref="B2:B53 G2:G48 G50:G53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/packlista.xlsx
+++ b/packlista.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edap\italy26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BFED1A5-34EE-4281-B90B-5EA3CFBBBC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{733C9CF3-EBBF-48AF-A3AF-26AD55E92C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
+    <workbookView xWindow="-105" yWindow="2040" windowWidth="29010" windowHeight="15345" xr2:uid="{488FB7E8-4F4E-4281-B4E6-20B4B6AEE9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Packning" sheetId="1" r:id="rId1"/>
     <sheet name="Bingo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
   <si>
     <t>Cykel</t>
   </si>
@@ -67,12 +66,6 @@
     <t>Verktyg</t>
   </si>
   <si>
-    <t>Smörjmedel/Vax</t>
-  </si>
-  <si>
-    <t>Kedjelänksverktyg</t>
-  </si>
-  <si>
     <t>Multitool</t>
   </si>
   <si>
@@ -145,9 +138,6 @@
     <t>Kläder</t>
   </si>
   <si>
-    <t>Cykelbyxor</t>
-  </si>
-  <si>
     <t>Cykeltröjor</t>
   </si>
   <si>
@@ -244,24 +234,9 @@
     <t>Påsar</t>
   </si>
   <si>
-    <t>Ansiktskräm</t>
-  </si>
-  <si>
     <t>Penna + notes</t>
   </si>
   <si>
-    <t>Rakhyvel + parfym + skyddsfodral</t>
-  </si>
-  <si>
-    <t>Nagelklippare, pincett</t>
-  </si>
-  <si>
-    <t>Sovsäck, lätt</t>
-  </si>
-  <si>
-    <t>Handskar för meck, de tunna</t>
-  </si>
-  <si>
     <t>Övrigt</t>
   </si>
   <si>
@@ -283,9 +258,6 @@
     <t>Toptubebag</t>
   </si>
   <si>
-    <t>ej</t>
-  </si>
-  <si>
     <t>Reservdelar</t>
   </si>
   <si>
@@ -337,9 +309,6 @@
     <t>Ta en bild utanför Colosseum</t>
   </si>
   <si>
-    <t>Bestig ett berg</t>
-  </si>
-  <si>
     <t>Träffa en 100-åring</t>
   </si>
   <si>
@@ -388,13 +357,49 @@
     <t>Delta i en tävling</t>
   </si>
   <si>
-    <t>Delta i någonting udda</t>
-  </si>
-  <si>
     <t>Bli helt och hållet dyngsur av regn</t>
   </si>
   <si>
     <t>Ta en bild med kändis</t>
+  </si>
+  <si>
+    <t>Delta i en gudstjänst/mässa</t>
+  </si>
+  <si>
+    <t>Delta i något unikt evenemang</t>
+  </si>
+  <si>
+    <t>Pincett</t>
+  </si>
+  <si>
+    <t>KÖP</t>
+  </si>
+  <si>
+    <t>After-sun</t>
+  </si>
+  <si>
+    <t>FIXA</t>
+  </si>
+  <si>
+    <t>Stormkök</t>
+  </si>
+  <si>
+    <t>Vax</t>
+  </si>
+  <si>
+    <t>Sovsäck</t>
+  </si>
+  <si>
+    <t>Rakhyvel + skyddsfodral</t>
+  </si>
+  <si>
+    <t>Parfym</t>
+  </si>
+  <si>
+    <t>2xCykelbyxor</t>
+  </si>
+  <si>
+    <t>Bandage, plåster, etc</t>
   </si>
 </sst>
 </file>
@@ -784,743 +789,722 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61363B01-F3E6-4FE4-8E68-4A80D3197864}">
-  <dimension ref="A2:I75"/>
+  <dimension ref="A2:O75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>110</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
       <c r="B9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>65</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="E15" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" t="s">
+        <v>111</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
+        <v>118</v>
+      </c>
+      <c r="M15" t="s">
+        <v>113</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" t="s">
+        <v>111</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-      <c r="H17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" t="s">
+        <v>111</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" t="s">
+        <v>111</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19">
+        <v>72</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19">
         <v>3</v>
       </c>
-      <c r="H19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B20">
+      <c r="O19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="G20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H21" s="1" t="s">
+      <c r="K21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
         <v>9</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B24">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24">
         <v>1</v>
       </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36">
         <v>1</v>
       </c>
-      <c r="H26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="G36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>81</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50">
-        <v>2</v>
-      </c>
-      <c r="H50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51" t="s">
-        <v>70</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
@@ -1529,7 +1513,103 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B53 G2:G48 G50:G53">
+  <conditionalFormatting sqref="N3:N12 F38 B2:B19 F2 F4:F18 F20:F36 J19:J24 B21:B37 J2:J17">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N16">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N17">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N18">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N24">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25:N26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1555,87 +1635,87 @@
   <sheetData>
     <row r="2" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
